--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MISSOURI_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/MISSOURI_2018.xlsx
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C126">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C211">
@@ -4585,7 +4585,7 @@
         <v>39</v>
       </c>
       <c r="D235">
-        <v>0.009048723897911833</v>
+        <v>0.009048723897911832</v>
       </c>
     </row>
     <row r="236">
@@ -9157,7 +9157,7 @@
         <v>39</v>
       </c>
       <c r="D489">
-        <v>0.009048723897911833</v>
+        <v>0.009048723897911832</v>
       </c>
     </row>
     <row r="490">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C524">
